--- a/artfynd/A 9092-2025 artfynd.xlsx
+++ b/artfynd/A 9092-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1434938</v>
+        <v>130634</v>
       </c>
       <c r="B2" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592311.472316712</v>
+        <v>592192</v>
       </c>
       <c r="R2" t="n">
-        <v>6651909.926515322</v>
+        <v>6651618</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,14 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547297 - 6652799. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,73 +761,78 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>under gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
+          <t>VBSK fynddatabas</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1156985</v>
+        <v>163956</v>
       </c>
       <c r="B3" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592311.472316712</v>
+        <v>592146</v>
       </c>
       <c r="R3" t="n">
-        <v>6651909.926515322</v>
+        <v>6651692</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +859,14 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547252 - 6652874. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,35 +877,45 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>under gran</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>RGC08-106</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
+          <t>VBSK fynddatabas</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1741391</v>
+        <v>1354329</v>
       </c>
       <c r="B4" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592311.472316712</v>
+        <v>592311</v>
       </c>
       <c r="R4" t="n">
-        <v>6651909.926515322</v>
+        <v>6651910</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -980,19 +980,9 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1354329</v>
+        <v>1354333</v>
       </c>
       <c r="B5" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,17 +1044,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592311.472316712</v>
+        <v>592294</v>
       </c>
       <c r="R5" t="n">
-        <v>6651909.926515322</v>
+        <v>6651846</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1081,14 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547401 - 6653026. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,73 +1099,73 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
+          <t>VBSK fynddatabas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>163956</v>
+        <v>1354334</v>
       </c>
       <c r="B6" t="n">
-        <v>85128</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>426</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592146.450985281</v>
+        <v>592311</v>
       </c>
       <c r="R6" t="n">
-        <v>6651692.076374148</v>
+        <v>6651914</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,24 +1192,14 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547252 - 6652874. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
+          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Kalkbarrskog norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,17 +1213,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>under gran</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>RGC08-106</t>
+          <t>Kalkbarrskog norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,53 +1235,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1354333</v>
+        <v>1156985</v>
       </c>
       <c r="B7" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592293.5205472865</v>
+        <v>592311</v>
       </c>
       <c r="R7" t="n">
-        <v>6651845.911623385</v>
+        <v>6651910</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,26 +1303,11 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547401 - 6653026. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1376,78 +1316,68 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>VBSK fynddatabas</t>
+          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130634</v>
+        <v>1156987</v>
       </c>
       <c r="B8" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Saladamm - Armanbo - kalkbrott, kalkbarrskog - kalkbrott, Vstm</t>
+          <t>Saladamm - Armanbo - kalkbarrskog, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592192.4325577235</v>
+        <v>592311</v>
       </c>
       <c r="R8" t="n">
-        <v>6651617.642210816</v>
+        <v>6651914</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,24 +1404,14 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Koordinater = 1547297 - 6652799. gran och tallskog i området runt kalkbrottet norr om Armanbo i Sala socken.</t>
+          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Kalkbarrskog norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,12 +1425,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>kalkbarrskog/gran och tallskog i området runt kalkbrottet norr om Armanbo i</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>under gran</t>
+          <t>Kalkbarrskog norr om Armanbo i Sala socken.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,15 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1156987</v>
+        <v>1434938</v>
       </c>
       <c r="B9" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592311.3722048032</v>
+        <v>592311</v>
       </c>
       <c r="R9" t="n">
-        <v>6651913.928121007</v>
+        <v>6651910</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,26 +1515,11 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Kalkbarrskog norr om Armanbo i Sala socken.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1633,62 +1528,52 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog norr om Armanbo i Sala socken.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>VBSK fynddatabas</t>
+          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1741601</v>
+        <v>1434941</v>
       </c>
       <c r="B10" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1698,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592311.3722048032</v>
+        <v>592311</v>
       </c>
       <c r="R10" t="n">
-        <v>6651913.928121007</v>
+        <v>6651914</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1731,19 +1616,9 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1784,15 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1434941</v>
+        <v>1741391</v>
       </c>
       <c r="B11" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,13 +1694,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592311.3722048032</v>
+        <v>592311</v>
       </c>
       <c r="R11" t="n">
-        <v>6651913.928121007</v>
+        <v>6651910</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,26 +1727,11 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>leg. Kurt-Anders Johansson,Rolf-Göran Carlsson. Kalkbarrskog norr om Armanbo i Sala socken.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1885,62 +1740,52 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog norr om Armanbo i Sala socken.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>VBSK fynddatabas</t>
+          <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1354334</v>
+        <v>1741601</v>
       </c>
       <c r="B12" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1950,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592311.3722048032</v>
+        <v>592311</v>
       </c>
       <c r="R12" t="n">
-        <v>6651913.928121007</v>
+        <v>6651914</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -1983,19 +1828,9 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2039,12 +1874,7 @@
         <v>83573961</v>
       </c>
       <c r="B13" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592088.9009477166</v>
+        <v>592089</v>
       </c>
       <c r="R13" t="n">
-        <v>6651526.958914966</v>
+        <v>6651527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2118,19 +1948,9 @@
           <t>2013-08-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 9092-2025 artfynd.xlsx
+++ b/artfynd/A 9092-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/163956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1354329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1354333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1354334</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
           <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1156985</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1156987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
           <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1434938</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1434941</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
           <t>Inventering violgubbe-fjälltaggsvampar U-län 2008</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1741391</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1741601</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,8 +2043,27 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83573961</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>